--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/28.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/28.xlsx
@@ -426,13 +426,13 @@
         <v>-11.72466997064806</v>
       </c>
       <c r="E2">
-        <v>-4.630561473932873</v>
+        <v>-5.137460740455461</v>
       </c>
       <c r="F2">
-        <v>-3.656151270737838</v>
+        <v>-3.451132823647169</v>
       </c>
       <c r="G2">
-        <v>-7.188738230647381</v>
+        <v>-6.714164906501778</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.44032911024507</v>
       </c>
       <c r="E3">
-        <v>-5.332823637620368</v>
+        <v>-5.034270403242677</v>
       </c>
       <c r="F3">
-        <v>-3.485502615556723</v>
+        <v>-3.213472559049185</v>
       </c>
       <c r="G3">
-        <v>-7.348237004183928</v>
+        <v>-6.942125761790453</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.34364940971404</v>
       </c>
       <c r="E4">
-        <v>-6.055264681486044</v>
+        <v>-6.106454551668749</v>
       </c>
       <c r="F4">
-        <v>-3.401902120531391</v>
+        <v>-3.085407786943784</v>
       </c>
       <c r="G4">
-        <v>-6.66627786527622</v>
+        <v>-6.263430820784467</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.30583339217632</v>
       </c>
       <c r="E5">
-        <v>-6.146563245954686</v>
+        <v>-6.214494884543749</v>
       </c>
       <c r="F5">
-        <v>-3.569586048777887</v>
+        <v>-3.186746941532665</v>
       </c>
       <c r="G5">
-        <v>-6.161413049446286</v>
+        <v>-5.735484881454734</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.31282125287795</v>
       </c>
       <c r="E6">
-        <v>-7.229937253653711</v>
+        <v>-7.975967118625341</v>
       </c>
       <c r="F6">
-        <v>-3.357987051039379</v>
+        <v>-3.034431713710308</v>
       </c>
       <c r="G6">
-        <v>-6.622926271439464</v>
+        <v>-5.762545280692736</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.31293247835944</v>
       </c>
       <c r="E7">
-        <v>-8.688382121038034</v>
+        <v>-8.588071893294128</v>
       </c>
       <c r="F7">
-        <v>-3.487038408721514</v>
+        <v>-2.843746507790279</v>
       </c>
       <c r="G7">
-        <v>-5.133392653681944</v>
+        <v>-6.18120018013451</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.27072606564717</v>
       </c>
       <c r="E8">
-        <v>-8.556064639007914</v>
+        <v>-7.214458929495493</v>
       </c>
       <c r="F8">
-        <v>-3.197176087133911</v>
+        <v>-2.966378018100718</v>
       </c>
       <c r="G8">
-        <v>-6.674504570941309</v>
+        <v>-5.599639955796279</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.12794711763801</v>
       </c>
       <c r="E9">
-        <v>-9.509611825381038</v>
+        <v>-9.15611914434229</v>
       </c>
       <c r="F9">
-        <v>-3.178288481982679</v>
+        <v>-2.637588227153358</v>
       </c>
       <c r="G9">
-        <v>-5.179412547223352</v>
+        <v>-6.284326984228347</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.82837535347092</v>
       </c>
       <c r="E10">
-        <v>-10.02636052287031</v>
+        <v>-9.541370013596831</v>
       </c>
       <c r="F10">
-        <v>-3.131063256349079</v>
+        <v>-2.599774911950366</v>
       </c>
       <c r="G10">
-        <v>-5.358466713260373</v>
+        <v>-5.866757943723454</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.31158277359637</v>
       </c>
       <c r="E11">
-        <v>-11.69901579623946</v>
+        <v>-9.76782994177241</v>
       </c>
       <c r="F11">
-        <v>-3.306046758149044</v>
+        <v>-2.598670698202434</v>
       </c>
       <c r="G11">
-        <v>-5.044309183765695</v>
+        <v>-6.051618806636357</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.53063780240363</v>
       </c>
       <c r="E12">
-        <v>-10.5195068138316</v>
+        <v>-10.45658366749502</v>
       </c>
       <c r="F12">
-        <v>-3.015576414887786</v>
+        <v>-2.25164357051504</v>
       </c>
       <c r="G12">
-        <v>-5.062590016233551</v>
+        <v>-5.079685673398347</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.45156796721881</v>
       </c>
       <c r="E13">
-        <v>-10.94677286492931</v>
+        <v>-11.54847573480248</v>
       </c>
       <c r="F13">
-        <v>-2.584303493968279</v>
+        <v>-2.345245773561773</v>
       </c>
       <c r="G13">
-        <v>-4.859689990677158</v>
+        <v>-4.421234718365004</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.06581152449162</v>
       </c>
       <c r="E14">
-        <v>-12.82031577375273</v>
+        <v>-11.7740163827545</v>
       </c>
       <c r="F14">
-        <v>-2.277450528581856</v>
+        <v>-1.88957411916021</v>
       </c>
       <c r="G14">
-        <v>-3.952103931085963</v>
+        <v>-4.084337051561072</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.38477260020989</v>
       </c>
       <c r="E15">
-        <v>-12.54531966116294</v>
+        <v>-11.06808615512079</v>
       </c>
       <c r="F15">
-        <v>-2.186745954710116</v>
+        <v>-1.878165843288855</v>
       </c>
       <c r="G15">
-        <v>-4.028057777393462</v>
+        <v>-3.873822771264356</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.44107502796934</v>
       </c>
       <c r="E16">
-        <v>-14.21006369044069</v>
+        <v>-12.09461422860153</v>
       </c>
       <c r="F16">
-        <v>-1.823365197756654</v>
+        <v>-1.658081878243471</v>
       </c>
       <c r="G16">
-        <v>-2.861974390459354</v>
+        <v>-3.48888577814006</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.28378701149122</v>
       </c>
       <c r="E17">
-        <v>-13.63666831158947</v>
+        <v>-13.33753090406479</v>
       </c>
       <c r="F17">
-        <v>-1.863037369411527</v>
+        <v>-1.390538259589495</v>
       </c>
       <c r="G17">
-        <v>-1.965296578420056</v>
+        <v>-2.5591488583456</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.97802890355204</v>
       </c>
       <c r="E18">
-        <v>-14.69298468709267</v>
+        <v>-13.88380978055808</v>
       </c>
       <c r="F18">
-        <v>-1.346451718045103</v>
+        <v>-1.104799550933028</v>
       </c>
       <c r="G18">
-        <v>-1.692070633972927</v>
+        <v>-2.18881137104949</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.60217251997766</v>
       </c>
       <c r="E19">
-        <v>-15.59899195333327</v>
+        <v>-14.72009213250258</v>
       </c>
       <c r="F19">
-        <v>-1.228060620469595</v>
+        <v>-0.6354184160151329</v>
       </c>
       <c r="G19">
-        <v>-1.919352827426051</v>
+        <v>-2.008217801336707</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.23782088573968</v>
       </c>
       <c r="E20">
-        <v>-17.29526321865242</v>
+        <v>-15.42973570882258</v>
       </c>
       <c r="F20">
-        <v>-0.9897517441952186</v>
+        <v>-0.5756202299418423</v>
       </c>
       <c r="G20">
-        <v>-2.343592617192575</v>
+        <v>-2.169702902196816</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.96508054117062</v>
       </c>
       <c r="E21">
-        <v>-17.7137168593312</v>
+        <v>-15.77520846239374</v>
       </c>
       <c r="F21">
-        <v>-0.7644730871668791</v>
+        <v>-0.02659239761217748</v>
       </c>
       <c r="G21">
-        <v>-2.3745495285303</v>
+        <v>-1.565816358741742</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.849757950794746</v>
       </c>
       <c r="E22">
-        <v>-17.93871861887631</v>
+        <v>-16.88950289061714</v>
       </c>
       <c r="F22">
-        <v>-0.3968933358486265</v>
+        <v>0.213254756929197</v>
       </c>
       <c r="G22">
-        <v>-1.387824877822826</v>
+        <v>-1.988520055378044</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.940400079563169</v>
       </c>
       <c r="E23">
-        <v>-17.79406104517529</v>
+        <v>-17.26440619676416</v>
       </c>
       <c r="F23">
-        <v>-0.7342269081884607</v>
+        <v>-0.006227813381754435</v>
       </c>
       <c r="G23">
-        <v>-1.463477464486251</v>
+        <v>-1.844666920060093</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.264503826985246</v>
       </c>
       <c r="E24">
-        <v>-18.24742016350519</v>
+        <v>-18.38869496712248</v>
       </c>
       <c r="F24">
-        <v>-0.02680445966729415</v>
+        <v>0.1540563088555331</v>
       </c>
       <c r="G24">
-        <v>-2.464013711183564</v>
+        <v>-2.094222463901434</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.832869727426551</v>
       </c>
       <c r="E25">
-        <v>-18.0450381316284</v>
+        <v>-18.20368416153911</v>
       </c>
       <c r="F25">
-        <v>-0.4201124741490966</v>
+        <v>0.1987376181951356</v>
       </c>
       <c r="G25">
-        <v>-2.285856702987685</v>
+        <v>-2.699658342668887</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.640985621589608</v>
       </c>
       <c r="E26">
-        <v>-18.97174505255806</v>
+        <v>-18.07505285735123</v>
       </c>
       <c r="F26">
-        <v>-0.3059808417587835</v>
+        <v>0.1391838005056708</v>
       </c>
       <c r="G26">
-        <v>-1.606466547418452</v>
+        <v>-2.268251221809841</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.668767316824602</v>
       </c>
       <c r="E27">
-        <v>-19.14802043178063</v>
+        <v>-18.01243311877317</v>
       </c>
       <c r="F27">
-        <v>-0.1894933324749087</v>
+        <v>0.1846023568337649</v>
       </c>
       <c r="G27">
-        <v>-2.877096962482744</v>
+        <v>-2.386457560835058</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.886997873831538</v>
       </c>
       <c r="E28">
-        <v>-19.73910403010581</v>
+        <v>-18.29397287630404</v>
       </c>
       <c r="F28">
-        <v>0.08588498507474499</v>
+        <v>0.3339934477242389</v>
       </c>
       <c r="G28">
-        <v>-3.42447249358246</v>
+        <v>-2.801295401270052</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.255781899351806</v>
       </c>
       <c r="E29">
-        <v>-19.36093116572527</v>
+        <v>-18.20205843937036</v>
       </c>
       <c r="F29">
-        <v>0.1260955955414386</v>
+        <v>0.2474663306648165</v>
       </c>
       <c r="G29">
-        <v>-2.651420383616167</v>
+        <v>-3.354325344150843</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.730776275773767</v>
       </c>
       <c r="E30">
-        <v>-20.01265103101315</v>
+        <v>-18.17232900751</v>
       </c>
       <c r="F30">
-        <v>-0.2518462036184331</v>
+        <v>0.271498097387433</v>
       </c>
       <c r="G30">
-        <v>-3.538636656504227</v>
+        <v>-2.646805483134423</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.263150729166336</v>
       </c>
       <c r="E31">
-        <v>-18.07265729460118</v>
+        <v>-18.82131820297126</v>
       </c>
       <c r="F31">
-        <v>-0.2941699793296682</v>
+        <v>-0.08224046299744267</v>
       </c>
       <c r="G31">
-        <v>-3.414007859132824</v>
+        <v>-2.788884166043324</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.802096915793578</v>
       </c>
       <c r="E32">
-        <v>-19.55950927943562</v>
+        <v>-18.49025958216652</v>
       </c>
       <c r="F32">
-        <v>-0.3903989354106783</v>
+        <v>-0.03970793870070206</v>
       </c>
       <c r="G32">
-        <v>-3.205950003626248</v>
+        <v>-2.558162315774898</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.29764055384356</v>
       </c>
       <c r="E33">
-        <v>-18.70683838005736</v>
+        <v>-17.20488393440734</v>
       </c>
       <c r="F33">
-        <v>-0.4442444733274518</v>
+        <v>-0.1301143003074345</v>
       </c>
       <c r="G33">
-        <v>-2.760804118779226</v>
+        <v>-2.21192891055022</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.71160118653599</v>
       </c>
       <c r="E34">
-        <v>-16.9674062289711</v>
+        <v>-17.51882039498908</v>
       </c>
       <c r="F34">
-        <v>-0.5218227373344311</v>
+        <v>-0.003027830104739945</v>
       </c>
       <c r="G34">
-        <v>-2.926669071387791</v>
+        <v>-2.136719936989058</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.02728769789655</v>
       </c>
       <c r="E35">
-        <v>-18.11739861779696</v>
+        <v>-16.32681735279406</v>
       </c>
       <c r="F35">
-        <v>-0.1590466885850128</v>
+        <v>-0.1208349286612744</v>
       </c>
       <c r="G35">
-        <v>-3.293649665507081</v>
+        <v>-2.149078203487157</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.24885524845594</v>
       </c>
       <c r="E36">
-        <v>-18.46150377221781</v>
+        <v>-17.27403373250446</v>
       </c>
       <c r="F36">
-        <v>0.1798185350825977</v>
+        <v>-0.1895272955384234</v>
       </c>
       <c r="G36">
-        <v>-2.111106246151716</v>
+        <v>-1.428786257780228</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.39571351302408</v>
       </c>
       <c r="E37">
-        <v>-17.52070876865028</v>
+        <v>-16.17683429366002</v>
       </c>
       <c r="F37">
-        <v>-0.2326968343679169</v>
+        <v>-0.003281310529996594</v>
       </c>
       <c r="G37">
-        <v>-2.573708637627315</v>
+        <v>-1.708752472945314</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.49162833108584</v>
       </c>
       <c r="E38">
-        <v>-17.24234347139879</v>
+        <v>-16.37970540072964</v>
       </c>
       <c r="F38">
-        <v>-0.4147802731772762</v>
+        <v>-0.1858949044771476</v>
       </c>
       <c r="G38">
-        <v>-1.799603774179533</v>
+        <v>-1.271925989038481</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.55474907518511</v>
       </c>
       <c r="E39">
-        <v>-15.9991777298651</v>
+        <v>-16.09408095964385</v>
       </c>
       <c r="F39">
-        <v>-0.2340197371101877</v>
+        <v>-0.08215182768534313</v>
       </c>
       <c r="G39">
-        <v>-2.172000420801071</v>
+        <v>-0.5948167993458059</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.5939362299979</v>
       </c>
       <c r="E40">
-        <v>-17.55097256044354</v>
+        <v>-15.78595453121395</v>
       </c>
       <c r="F40">
-        <v>-0.3342555063185391</v>
+        <v>-0.2514817219612013</v>
       </c>
       <c r="G40">
-        <v>-1.562231037922711</v>
+        <v>-1.324566973658432</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.6093911248246</v>
       </c>
       <c r="E41">
-        <v>-15.58219584323882</v>
+        <v>-14.74964495387664</v>
       </c>
       <c r="F41">
-        <v>-0.2990258690448789</v>
+        <v>-0.2043683259269794</v>
       </c>
       <c r="G41">
-        <v>-1.630024389475906</v>
+        <v>-0.8970166383526369</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.59461246101423</v>
       </c>
       <c r="E42">
-        <v>-15.28147799828546</v>
+        <v>-15.11950353997911</v>
       </c>
       <c r="F42">
-        <v>-0.5848871760769603</v>
+        <v>-0.4217435295652088</v>
       </c>
       <c r="G42">
-        <v>-1.682764690462035</v>
+        <v>-0.4905511675864599</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.54201248886393</v>
       </c>
       <c r="E43">
-        <v>-16.10108650893372</v>
+        <v>-15.2694594282691</v>
       </c>
       <c r="F43">
-        <v>-0.3108027684104794</v>
+        <v>-0.4851641662909418</v>
       </c>
       <c r="G43">
-        <v>-1.929635381871027</v>
+        <v>-0.5758870999522533</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.44323898857689</v>
       </c>
       <c r="E44">
-        <v>-14.85498178776906</v>
+        <v>-14.50404316607064</v>
       </c>
       <c r="F44">
-        <v>-0.3543003407314815</v>
+        <v>-0.3969529783016281</v>
       </c>
       <c r="G44">
-        <v>-1.834013584514718</v>
+        <v>-0.7478136614432238</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.29208618707891</v>
       </c>
       <c r="E45">
-        <v>-14.73240052485543</v>
+        <v>-13.29364093398245</v>
       </c>
       <c r="F45">
-        <v>-0.760317167907034</v>
+        <v>-0.4069836791821272</v>
       </c>
       <c r="G45">
-        <v>-1.416914641476402</v>
+        <v>-0.5911222305239793</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.08629766516768</v>
       </c>
       <c r="E46">
-        <v>-14.94404781455192</v>
+        <v>-13.31550893496549</v>
       </c>
       <c r="F46">
-        <v>-0.6285934969834678</v>
+        <v>-0.3485564411604697</v>
       </c>
       <c r="G46">
-        <v>-1.221304437197485</v>
+        <v>-0.284085684484273</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.82990187801501</v>
       </c>
       <c r="E47">
-        <v>-14.14068294016917</v>
+        <v>-13.75988808933818</v>
       </c>
       <c r="F47">
-        <v>-1.023568186679703</v>
+        <v>-0.7153624973245076</v>
       </c>
       <c r="G47">
-        <v>-1.754212884290586</v>
+        <v>-1.337951509273706</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.53326749496578</v>
       </c>
       <c r="E48">
-        <v>-13.55761021236356</v>
+        <v>-13.02836745508713</v>
       </c>
       <c r="F48">
-        <v>-0.7068775300176323</v>
+        <v>-0.8836105437723096</v>
       </c>
       <c r="G48">
-        <v>-1.853598771925046</v>
+        <v>-0.3926980625366821</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.20944128718296</v>
       </c>
       <c r="E49">
-        <v>-13.00717872520524</v>
+        <v>-13.00598773654122</v>
       </c>
       <c r="F49">
-        <v>-1.147239298080655</v>
+        <v>-0.9865633580618434</v>
       </c>
       <c r="G49">
-        <v>-1.128059611538373</v>
+        <v>-0.5805086215250759</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.875004810490836</v>
       </c>
       <c r="E50">
-        <v>-12.87506955297947</v>
+        <v>-13.33067479441718</v>
       </c>
       <c r="F50">
-        <v>-0.9674570639162727</v>
+        <v>-1.076134725326554</v>
       </c>
       <c r="G50">
-        <v>-1.949554934380822</v>
+        <v>-0.5939163309591241</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.545163561362868</v>
       </c>
       <c r="E51">
-        <v>-12.98533336659224</v>
+        <v>-11.97927399562617</v>
       </c>
       <c r="F51">
-        <v>-1.160217330180315</v>
+        <v>-1.397477493322747</v>
       </c>
       <c r="G51">
-        <v>-1.439760716242912</v>
+        <v>-0.5483731559753704</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.23551668782069</v>
       </c>
       <c r="E52">
-        <v>-12.51576231131487</v>
+        <v>-12.41403014273256</v>
       </c>
       <c r="F52">
-        <v>-1.29791187334326</v>
+        <v>-1.157583121839413</v>
       </c>
       <c r="G52">
-        <v>-1.24085982969796</v>
+        <v>-0.7885499243039558</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.960056142497335</v>
       </c>
       <c r="E53">
-        <v>-12.98576810009697</v>
+        <v>-11.65642096972332</v>
       </c>
       <c r="F53">
-        <v>-1.241824773234511</v>
+        <v>-1.258716841312399</v>
       </c>
       <c r="G53">
-        <v>-1.269883382440751</v>
+        <v>-0.5454631864463511</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.732954644831272</v>
       </c>
       <c r="E54">
-        <v>-12.66962174419948</v>
+        <v>-12.0268773143948</v>
       </c>
       <c r="F54">
-        <v>-1.320194956478567</v>
+        <v>-1.494522391295514</v>
       </c>
       <c r="G54">
-        <v>-1.0690690005741</v>
+        <v>-0.8732237475618949</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.569083844917129</v>
       </c>
       <c r="E55">
-        <v>-10.92787101442129</v>
+        <v>-10.98483468896378</v>
       </c>
       <c r="F55">
-        <v>-1.62625765936272</v>
+        <v>-1.316078798854056</v>
       </c>
       <c r="G55">
-        <v>-1.912228533425539</v>
+        <v>-0.9058690371246481</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.482127452564908</v>
       </c>
       <c r="E56">
-        <v>-11.40651713161003</v>
+        <v>-11.35783603602757</v>
       </c>
       <c r="F56">
-        <v>-1.363056342634219</v>
+        <v>-1.727311855565037</v>
       </c>
       <c r="G56">
-        <v>-2.7204982268386</v>
+        <v>-0.6914714869103675</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.48426311206836</v>
       </c>
       <c r="E57">
-        <v>-10.59657238449414</v>
+        <v>-10.43705235909994</v>
       </c>
       <c r="F57">
-        <v>-1.550562274462304</v>
+        <v>-1.309556233924413</v>
       </c>
       <c r="G57">
-        <v>-2.149362910403534</v>
+        <v>-0.8049437458144267</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.581151618583476</v>
       </c>
       <c r="E58">
-        <v>-10.40640817549004</v>
+        <v>-11.0879299282224</v>
       </c>
       <c r="F58">
-        <v>-1.136415021228274</v>
+        <v>-1.661676992771621</v>
       </c>
       <c r="G58">
-        <v>-1.985666365123192</v>
+        <v>-1.054658195841652</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.77395585294455</v>
       </c>
       <c r="E59">
-        <v>-10.51911736506695</v>
+        <v>-10.80771248510177</v>
       </c>
       <c r="F59">
-        <v>-1.34410163972336</v>
+        <v>-1.714699133490012</v>
       </c>
       <c r="G59">
-        <v>-2.070019065463822</v>
+        <v>-1.390863958627877</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.054169089165809</v>
       </c>
       <c r="E60">
-        <v>-10.10442235781453</v>
+        <v>-9.734826423204508</v>
       </c>
       <c r="F60">
-        <v>-1.790695215757644</v>
+        <v>-1.893564364939495</v>
       </c>
       <c r="G60">
-        <v>-1.578264009969401</v>
+        <v>-0.9907183192961686</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.40839495269525</v>
       </c>
       <c r="E61">
-        <v>-10.5430005369834</v>
+        <v>-9.97401136334164</v>
       </c>
       <c r="F61">
-        <v>-1.796779574331206</v>
+        <v>-2.092819031641485</v>
       </c>
       <c r="G61">
-        <v>-2.506213235172654</v>
+        <v>-1.816484245884277</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.821177503318443</v>
       </c>
       <c r="E62">
-        <v>-9.469743140217508</v>
+        <v>-9.774917003594414</v>
       </c>
       <c r="F62">
-        <v>-1.734308246649082</v>
+        <v>-1.945356380064728</v>
       </c>
       <c r="G62">
-        <v>-2.464894316297011</v>
+        <v>-1.719342908125443</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.27661707733341</v>
       </c>
       <c r="E63">
-        <v>-10.44763540285587</v>
+        <v>-9.181360858461044</v>
       </c>
       <c r="F63">
-        <v>-1.689158909726897</v>
+        <v>-2.016200845454351</v>
       </c>
       <c r="G63">
-        <v>-2.920670362870632</v>
+        <v>-2.20825420500163</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.75963820783126</v>
       </c>
       <c r="E64">
-        <v>-9.693812034117038</v>
+        <v>-9.533114605480847</v>
       </c>
       <c r="F64">
-        <v>-1.934560267704042</v>
+        <v>-2.096688335779961</v>
       </c>
       <c r="G64">
-        <v>-2.68751526163084</v>
+        <v>-1.664417647083394</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.25368052380298</v>
       </c>
       <c r="E65">
-        <v>-8.831291703772095</v>
+        <v>-9.920059124014257</v>
       </c>
       <c r="F65">
-        <v>-2.150007860395958</v>
+        <v>-2.298995536361268</v>
       </c>
       <c r="G65">
-        <v>-2.472194069211104</v>
+        <v>-2.008406502432446</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.74457381980132</v>
       </c>
       <c r="E66">
-        <v>-9.710626258107517</v>
+        <v>-9.674615832798523</v>
       </c>
       <c r="F66">
-        <v>-1.659373303024435</v>
+        <v>-2.287887129489727</v>
       </c>
       <c r="G66">
-        <v>-3.283535948884607</v>
+        <v>-1.898377210889229</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.21642050232474</v>
       </c>
       <c r="E67">
-        <v>-8.561698060673455</v>
+        <v>-9.188085642362434</v>
       </c>
       <c r="F67">
-        <v>-2.143529198938662</v>
+        <v>-2.093729407417162</v>
       </c>
       <c r="G67">
-        <v>-2.868674934630838</v>
+        <v>-1.845425034988586</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.65498431839662</v>
       </c>
       <c r="E68">
-        <v>-9.354276109969929</v>
+        <v>-9.304055333224865</v>
       </c>
       <c r="F68">
-        <v>-2.284401359458746</v>
+        <v>-1.867495642773394</v>
       </c>
       <c r="G68">
-        <v>-2.763224127568433</v>
+        <v>-2.300350271358615</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.04929046429317</v>
       </c>
       <c r="E69">
-        <v>-8.968581450262638</v>
+        <v>-8.459327377256059</v>
       </c>
       <c r="F69">
-        <v>-1.678797690252681</v>
+        <v>-2.263374081306084</v>
       </c>
       <c r="G69">
-        <v>-2.884492721217476</v>
+        <v>-1.981442109015082</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.39359230556585</v>
       </c>
       <c r="E70">
-        <v>-9.312763588741616</v>
+        <v>-8.678609674129481</v>
       </c>
       <c r="F70">
-        <v>-2.106739745845531</v>
+        <v>-2.335036973689672</v>
       </c>
       <c r="G70">
-        <v>-2.719081313347791</v>
+        <v>-2.573473588894027</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.68588877405124</v>
       </c>
       <c r="E71">
-        <v>-8.674072143173795</v>
+        <v>-8.97563228429258</v>
       </c>
       <c r="F71">
-        <v>-2.420691819873946</v>
+        <v>-2.562521573111666</v>
       </c>
       <c r="G71">
-        <v>-2.200308895707379</v>
+        <v>-1.751206908940928</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.9260222811678</v>
       </c>
       <c r="E72">
-        <v>-9.626618536791225</v>
+        <v>-8.293558057731278</v>
       </c>
       <c r="F72">
-        <v>-2.355812428151884</v>
+        <v>-2.601378631242186</v>
       </c>
       <c r="G72">
-        <v>-2.316151505217556</v>
+        <v>-1.341536830092736</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.11564967472217</v>
       </c>
       <c r="E73">
-        <v>-8.970279628015513</v>
+        <v>-8.668167013067794</v>
       </c>
       <c r="F73">
-        <v>-2.055713970567887</v>
+        <v>-2.373784687323021</v>
       </c>
       <c r="G73">
-        <v>-2.685048905204084</v>
+        <v>-1.730204808039791</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.2568091386437</v>
       </c>
       <c r="E74">
-        <v>-9.030236623877069</v>
+        <v>-8.519968172692774</v>
       </c>
       <c r="F74">
-        <v>-2.141372958589175</v>
+        <v>-2.537962136353467</v>
       </c>
       <c r="G74">
-        <v>-2.777721006484902</v>
+        <v>-1.006079250598387</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.35183438030062</v>
       </c>
       <c r="E75">
-        <v>-8.843885389987426</v>
+        <v>-9.296030877283274</v>
       </c>
       <c r="F75">
-        <v>-2.238213249813452</v>
+        <v>-2.534814340222828</v>
       </c>
       <c r="G75">
-        <v>-1.761267656834773</v>
+        <v>-1.031524103613225</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.40337704229188</v>
       </c>
       <c r="E76">
-        <v>-9.289174767635661</v>
+        <v>-9.07708368748642</v>
       </c>
       <c r="F76">
-        <v>-2.407953185953696</v>
+        <v>-2.632787009686732</v>
       </c>
       <c r="G76">
-        <v>-1.763843261264326</v>
+        <v>-0.9842826187678254</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.41441857401952</v>
       </c>
       <c r="E77">
-        <v>-10.69330058929798</v>
+        <v>-9.882042584719864</v>
       </c>
       <c r="F77">
-        <v>-2.361012090339256</v>
+        <v>-2.828521943294227</v>
       </c>
       <c r="G77">
-        <v>-3.048440867958803</v>
+        <v>-0.4995061932701884</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.39035856513073</v>
       </c>
       <c r="E78">
-        <v>-10.95043187192751</v>
+        <v>-10.32400353397246</v>
       </c>
       <c r="F78">
-        <v>-2.226182870022595</v>
+        <v>-2.863612414844217</v>
       </c>
       <c r="G78">
-        <v>-2.455297044778663</v>
+        <v>-0.7650814669760623</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.34438385290118</v>
       </c>
       <c r="E79">
-        <v>-11.32882210306043</v>
+        <v>-10.85052920684429</v>
       </c>
       <c r="F79">
-        <v>-2.86131121019924</v>
+        <v>-3.010885370285732</v>
       </c>
       <c r="G79">
-        <v>-2.313602385152317</v>
+        <v>-0.4435083154734163</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.29177807083289</v>
       </c>
       <c r="E80">
-        <v>-11.68468317600519</v>
+        <v>-11.3420905319029</v>
       </c>
       <c r="F80">
-        <v>-2.991175196303521</v>
+        <v>-2.77574665606187</v>
       </c>
       <c r="G80">
-        <v>-1.998795988731942</v>
+        <v>0.002650596308622307</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.24692681922337</v>
       </c>
       <c r="E81">
-        <v>-11.61575074466043</v>
+        <v>-12.42853484497913</v>
       </c>
       <c r="F81">
-        <v>-2.485057623806274</v>
+        <v>-3.10988024512469</v>
       </c>
       <c r="G81">
-        <v>-2.221777783529552</v>
+        <v>-0.4436771532959191</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.21852632528181</v>
       </c>
       <c r="E82">
-        <v>-13.0832570885341</v>
+        <v>-12.67828471497616</v>
       </c>
       <c r="F82">
-        <v>-2.890903807296849</v>
+        <v>-2.920975200753277</v>
       </c>
       <c r="G82">
-        <v>-1.343258313773157</v>
+        <v>0.4694308962547811</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.20967546536341</v>
       </c>
       <c r="E83">
-        <v>-14.28509144779978</v>
+        <v>-13.06003507382277</v>
       </c>
       <c r="F83">
-        <v>-2.996668928918887</v>
+        <v>-3.333348919377913</v>
       </c>
       <c r="G83">
-        <v>-1.005380725489601</v>
+        <v>0.02470214014570768</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.21667343284056</v>
       </c>
       <c r="E84">
-        <v>-15.03737966385001</v>
+        <v>-13.48986424120881</v>
       </c>
       <c r="F84">
-        <v>-2.638982369492269</v>
+        <v>-3.132859156878348</v>
       </c>
       <c r="G84">
-        <v>-1.262411481158616</v>
+        <v>-0.2959275058782461</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.22787246998168</v>
       </c>
       <c r="E85">
-        <v>-15.3828705313172</v>
+        <v>-14.68564403072623</v>
       </c>
       <c r="F85">
-        <v>-3.137278496972284</v>
+        <v>-3.634862228485891</v>
       </c>
       <c r="G85">
-        <v>-1.278477558660699</v>
+        <v>-0.03772812763386836</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.23075223655832</v>
       </c>
       <c r="E86">
-        <v>-15.86750329114407</v>
+        <v>-16.13129143056488</v>
       </c>
       <c r="F86">
-        <v>-3.463381064064962</v>
+        <v>-3.313266808431844</v>
       </c>
       <c r="G86">
-        <v>-1.658276585108046</v>
+        <v>0.3085416935917407</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.21136946470253</v>
       </c>
       <c r="E87">
-        <v>-17.80199040316272</v>
+        <v>-17.60117522329258</v>
       </c>
       <c r="F87">
-        <v>-3.286272799876817</v>
+        <v>-3.634748742151707</v>
       </c>
       <c r="G87">
-        <v>-2.274269793600236</v>
+        <v>-0.5256859873947449</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.16148744754296</v>
       </c>
       <c r="E88">
-        <v>-19.05764567600956</v>
+        <v>-18.21100217553551</v>
       </c>
       <c r="F88">
-        <v>-3.240711764355441</v>
+        <v>-3.721291598191783</v>
       </c>
       <c r="G88">
-        <v>-1.464205784504891</v>
+        <v>0.09764339001246974</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.07654149168937</v>
       </c>
       <c r="E89">
-        <v>-20.38909401832277</v>
+        <v>-19.82195246207614</v>
       </c>
       <c r="F89">
-        <v>-3.676537392520734</v>
+        <v>-3.766248753876518</v>
       </c>
       <c r="G89">
-        <v>-1.635341125611976</v>
+        <v>-0.5896622799411607</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.95938007522518</v>
       </c>
       <c r="E90">
-        <v>-22.0184027384905</v>
+        <v>-20.90844205989245</v>
       </c>
       <c r="F90">
-        <v>-3.428935062354351</v>
+        <v>-4.03490984015687</v>
       </c>
       <c r="G90">
-        <v>-1.405615749550869</v>
+        <v>0.295531249622405</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.82005387030332</v>
       </c>
       <c r="E91">
-        <v>-23.79601445393543</v>
+        <v>-22.54311249328526</v>
       </c>
       <c r="F91">
-        <v>-3.537264809455456</v>
+        <v>-3.787247039170082</v>
       </c>
       <c r="G91">
-        <v>-1.378164705939233</v>
+        <v>-0.4755577068391006</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.67259641167992</v>
       </c>
       <c r="E92">
-        <v>-25.76188389082724</v>
+        <v>-25.14753299305065</v>
       </c>
       <c r="F92">
-        <v>-3.695724038304376</v>
+        <v>-3.696431464066367</v>
       </c>
       <c r="G92">
-        <v>-2.441538417517452</v>
+        <v>-0.7084678277089858</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.53725842326908</v>
       </c>
       <c r="E93">
-        <v>-29.07014246323479</v>
+        <v>-27.32016349618466</v>
       </c>
       <c r="F93">
-        <v>-3.675540866535166</v>
+        <v>-4.040041576217213</v>
       </c>
       <c r="G93">
-        <v>-1.804519934305351</v>
+        <v>-0.7806211677374013</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.43852620544644</v>
       </c>
       <c r="E94">
-        <v>-29.2722392012491</v>
+        <v>-28.80009597273538</v>
       </c>
       <c r="F94">
-        <v>-3.748996345978412</v>
+        <v>-3.858036003943717</v>
       </c>
       <c r="G94">
-        <v>-2.525364741117338</v>
+        <v>-1.026101430019899</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.40576651755538</v>
       </c>
       <c r="E95">
-        <v>-32.39452240310964</v>
+        <v>-31.31693578519242</v>
       </c>
       <c r="F95">
-        <v>-3.258949101095475</v>
+        <v>-3.579969634171979</v>
       </c>
       <c r="G95">
-        <v>-2.228071130599707</v>
+        <v>-0.8600047392235851</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.46978324309079</v>
       </c>
       <c r="E96">
-        <v>-35.96089720124339</v>
+        <v>-32.58138988303616</v>
       </c>
       <c r="F96">
-        <v>-4.009087143109401</v>
+        <v>-3.991560545600969</v>
       </c>
       <c r="G96">
-        <v>-2.6495433042954</v>
+        <v>-1.567196856231617</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.63967518165597</v>
       </c>
       <c r="E97">
-        <v>-36.88853698781863</v>
+        <v>-36.5678825360465</v>
       </c>
       <c r="F97">
-        <v>-3.77862704797655</v>
+        <v>-3.986669036087438</v>
       </c>
       <c r="G97">
-        <v>-2.529526096860202</v>
+        <v>-1.494616455828636</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.93765528186325</v>
       </c>
       <c r="E98">
-        <v>-39.97348065724893</v>
+        <v>-38.02746178616975</v>
       </c>
       <c r="F98">
-        <v>-3.339691728581148</v>
+        <v>-3.777926249153782</v>
       </c>
       <c r="G98">
-        <v>-3.90142278942526</v>
+        <v>-2.829958104549062</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-14.33586561330976</v>
       </c>
       <c r="E99">
-        <v>-42.30225294416742</v>
+        <v>-40.9886332040224</v>
       </c>
       <c r="F99">
-        <v>-4.176453806640624</v>
+        <v>-4.148575101699407</v>
       </c>
       <c r="G99">
-        <v>-4.179664210364385</v>
+        <v>-2.550869183951883</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.85785830656505</v>
       </c>
       <c r="E100">
-        <v>-44.28248670061155</v>
+        <v>-43.49239025507128</v>
       </c>
       <c r="F100">
-        <v>-3.679015039422507</v>
+        <v>-4.018826258664115</v>
       </c>
       <c r="G100">
-        <v>-3.625899326373876</v>
+        <v>-2.88134439240963</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-15.42536487557667</v>
       </c>
       <c r="E101">
-        <v>-46.8163965958405</v>
+        <v>-45.29561275526659</v>
       </c>
       <c r="F101">
-        <v>-3.528509794375268</v>
+        <v>-3.991085062711762</v>
       </c>
       <c r="G101">
-        <v>-4.265308023465331</v>
+        <v>-2.76115172606085</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.11749900609663</v>
       </c>
       <c r="E102">
-        <v>-49.8003269919372</v>
+        <v>-48.55498645076133</v>
       </c>
       <c r="F102">
-        <v>-3.921168368813276</v>
+        <v>-3.800770137020784</v>
       </c>
       <c r="G102">
-        <v>-4.842236794594121</v>
+        <v>-3.685641431175564</v>
       </c>
     </row>
   </sheetData>
